--- a/approval_forms/030_project_addendum_submission_form--approval_forms.xlsx
+++ b/approval_forms/030_project_addendum_submission_form--approval_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'project_manager',_'label':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'project manager', 'label': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'client',_'label':_'client'}</t>
+          <t>client</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'client', 'label': 'Client'}</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'changes',_'label':_'changes'}</t>
+          <t>changes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'changes', 'label': 'Changes'}</t>
+          <t>Changes</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'additions',_'label':_'additions'}</t>
+          <t>additions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'additions', 'label': 'Additions'}</t>
+          <t>Additions</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'submitted',_'label':_'submitted'}</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'submitted', 'label': 'Submitted'}</t>
+          <t>Submitted</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'approved',_'label':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'approved', 'label': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rejected',_'label':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'rejected', 'label': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'project_manager',_'label':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'project_manager', 'label': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'client',_'label':_'client'}</t>
+          <t>client</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'client', 'label': 'Client'}</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'label': 'Chatjimmy'}</t>
+          <t>Chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'chatjimmy', 'label': 'Chatjimmy'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'approval_forms',_'label':_'approval_forms'}</t>
+          <t>approval_forms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'approval forms', 'label': 'Approval Forms'}</t>
+          <t>Approval Forms</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'project_management',_'label':_'project_management'}</t>
+          <t>project_management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'project management', 'label': 'Project Management'}</t>
+          <t>Project Management</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'project_manager',_'label':_'project_manager'}</t>
+          <t>project_manager</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'project_manager', 'label': 'Project Manager'}</t>
+          <t>Project Manager</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'client',_'label':_'client'}</t>
+          <t>client</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'client', 'label': 'Client'}</t>
+          <t>Client</t>
         </is>
       </c>
     </row>
